--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0096.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0096.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Những Đỉnh Cao Danh Vọng</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Peaks of Prestige</t>
+          <t>Đỉnh Cao Danh Vọng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vĩnh viễn</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Featured</t>
+          <t>Nổi bật</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Lặp Lại</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Combat</t>
+          <t>Chiến Đấu</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Leisure</t>
+          <t>Nhàn Hạ</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Thám Hiểm</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Bắt đầu mô phỏng</t>
+          <t>Bắt Đầu Mô Phỏng</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Motorbike Expansion Mô-đun</t>
+          <t>Mô-đun Mở Rộng Xe Máy</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Install</t>
+          <t>Lắp đặt</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Mô-đun Installed</t>
+          <t>Mô-đun đã cài đặt</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Installed</t>
+          <t>Đã lắp đặt</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Nhận Điểm Mod</t>
+          <t>Nhận Điểm Cải Tiến</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Chi tiết cấp độ Mô-đun</t>
+          <t>Chi tiết Cấp Độ Mô-đun</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Exploration Modules</t>
+          <t>Mô-đun Thám Hiểm</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Combat Mô-đun</t>
+          <t>Mô-đun Chiến Đấu</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Core Mô-đun</t>
+          <t>Mô-đun Cốt Lõi</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Motorbike Modding Tasks</t>
+          <t>Nhiệm Vụ Nâng Cấp Xe Máy</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Modding Points Progress</t>
+          <t>Tiến Độ Điểm Nâng Cấp</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Antivoid Tactics</t>
+          <t>Chiến Thuật Phòng Không</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Split-Second Mode</t>
+          <t>Chế Độ Phản Ứng Tức Thời</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 5 Điểm Mod Antivoid</t>
+          <t>Thu thập tổng cộng 5 Điểm Nâng Cấp Kháng Hư Không</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Vectored Thrust</t>
+          <t>Lực Đẩy Định Hướng</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 9 Điểm Mod Antivoid</t>
+          <t>Thu thập tổng cộng 9 Điểm Cải Tiến Kháng Hư Không.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ecoacoustics Scan</t>
+          <t>Quét Âm Sinh Học</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 12 Điểm Mod Antivoid</t>
+          <t>Thu thập tổng cộng 12 Điểm Cải Tiến Kháng Hư Không</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ram Dynamics</t>
+          <t>Động Lực Đâm</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Enhanced Ram</t>
+          <t>Húc Đâm Cường Hóa</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Antivoid Armor</t>
+          <t>Giáp Phòng Không</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Life Hỗ Trợ Mode</t>
+          <t>Chế Độ Hỗ Trợ Sinh Tồn</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Antivoid Off-Tuning Mô-đun</t>
+          <t>Mô-đun Giải Điều Phòng Không</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kinetics Conversion</t>
+          <t>Chuyển Hóa Động Năng</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Thường</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vehicle</t>
+          <t>Phương Tiện Giao Thông</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Antivoid Tactics</t>
+          <t>Chiến Thuật Phòng Không</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Motorbike Ride Share</t>
+          <t>Chia Sẻ Chuyến Đi Xe Máy</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Intimacy</t>
+          <t>Thân Tình</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Invite Companion</t>
+          <t>Mời Đồng Hành</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Solo Ride</t>
+          <t>Hành Trình Đơn Độc</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>(Giữ) Share Ride</t>
+          <t>(Giữ) Chia sẻ chuyến đi</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Rover sẽ tự động ngồi ghế lái khi chia sẻ phương tiện</t>
+          <t>Vận Mệnh Giả sẽ tự động ngồi vào ghế lái khi dùng chung phương tiện.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Không thể mời đồng hành khi đang ở Chế độ Hợp tác</t>
+          <t>Không thể mời Đồng Hành khi đang ở Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Số lần nhận miễn phí trong tuần này</t>
+          <t>Lượt nhận miễn phí trong tuần</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Số lần nhận miễn phí</t>
+          <t>Lượt nhận miễn phí</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Số lần nhận miễn phí trong tuần này:</t>
+          <t>Lượt nhận miễn phí trong tuần:</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Phần thưởng Tinh thể Tàn Dư</t>
+          <t>Phần Thưởng Pha Lê Tàn Tích</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Đạt cấp tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Echo Đặc biệt của khu vực</t>
+          <t>Echo Đặc Trưng Vùng Miền</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Other Echoes</t>
+          <t>Tiếng Vọng Khác</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Show Special Echoes</t>
+          <t>Hiển thị Tiếng Vọng Đặc Biệt</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Show Ordinary Echoes</t>
+          <t>Hiển thị Tiếng Vọng Thông Thường</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Ordinary Echo</t>
+          <t>Tiếng Vọng Bình Thường</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Special Echo</t>
+          <t>Echo Đặc Biệt</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Đã chuyển đổi ngoại hình Echo</t>
+          <t>Đã chuyển đổi Hiển Thị Echo</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Bạn không sở hữu ngoại hình Phantom này</t>
+          <t>Bạn không sở hữu Ngoại Hình Ảo này</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Có thể nhận qua</t>
+          <t>Có thể nhận thông qua</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Giữ để xem chi tiết Echo Máy chiếu</t>
+          <t>Giữ để xem chi tiết Echo Máy Chiếu</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Đạt 4.800 điểm trong Stability Accords</t>
+          <t>Đạt 4.800 điểm trong Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định.</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Đạt 45.000 điểm trong Singularity Expansion</t>
+          <t>Đạt 45.000 điểm trong Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tổng điểm</t>
+          <t>Tổng Điểm</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Điểm đội</t>
+          <t>Điểm Đội</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Resonators</t>
+          <t>Resonator</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Preset Teams</t>
+          <t>Đội Hình Cài Đặt</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Demo Resonators</t>
+          <t>Resonator Demo</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Hiệp ước Ổn định</t>
+          <t>Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Vui lòng chọn Power Circuit của bạn</t>
+          <t>Hãy chọn Mạch Năng Lượng của bạn.</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Bạn có muốn cập nhật bản ghi của Đội {1} về {0} không?</t>
+          <t>Bạn có muốn cập nhật kỷ lục của Đội {1} về {0} không?</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Điểm Hiện Tại</t>
+          <t>Điểm hiện tại</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Tổng điểm</t>
+          <t>Tổng Điểm</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Kỷ lục tốt nhất</t>
+          <t>Kỷ Lục Tốt Nhất</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Default Bubble</t>
+          <t>Bong bóng mặc định</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Pangu Terminal</t>
+          <t>Thiết bị đầu cuối Pangu</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Default Background</t>
+          <t>Hình nền mặc định</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>[Image]</t>
+          <t>[Hình Ảnh]</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Typing</t>
+          <t>Đang nhập...</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Apply</t>
+          <t>Áp dụng</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Bong Bóng Chat</t>
+          <t>Bong Bóng Trò Chuyện</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Hình Nền Chat</t>
+          <t>Hình Nền Trò Chuyện</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Hãy ủng hộ Dự án Huấn luyện Xe máy Trăm Ngày ε=ε=ε=ε=┌( *｀ω´)┘</t>
+          <t>Hãy ủng hộ Dự Án Huấn Luyện Xe Máy Trăm Ngày ε=ε=ε=ε=┌( *｀ω´)┘</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Unknown Duelist</t>
+          <t>Đối thủ bí ẩn</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Khi Âm Vang Vô Định</t>
+          <t>Khi Những Âm Thanh Vô Định Vang Lên</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Điều Gì Cháy Dưới Vùng Đất Băng Giá</t>
+          <t>Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Dấu Vết Ngôi Sao</t>
+          <t>Dấu Chân Sao Trời</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>An Unexpected Opening</t>
+          <t>Một cơ hội bất ngờ!</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Điều Gì Cháy Dưới Vùng Đất Băng Giá</t>
+          <t>Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mist</t>
+          <t>Sương mù</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Her Resolve</t>
+          <t>Nghị Lực Của Nàng</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>"Cùng Nhau Trở Về"</t>
+          <t>"Cùng trở về nào"</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>A New Tomorrow</t>
+          <t>Ngày Mai Mới</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Survivors</t>
+          <t>Những người sống sót</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>At Infinity's Edge</t>
+          <t>Tại Rìa Vô Cực</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Lahai-Roi Chương III: Khi Tiếng Vang Vô Định Rung Động</t>
+          <t>Chương III Lahai-Roi: Khi Điều Vô Định Rung Động</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Lahai-Roi Chương III: Điều Cháy Bên Dưới Vùng Đất Băng Giá</t>
+          <t>Chương III Lahai-Roi: What Burns Beneath Frostlands</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Lahai-Roi Chương III: Khúc Ca Bình Minh Thứ Hai</t>
+          <t>Chương III Lahai-Roi: Khúc Ca Bình Minh Thứ Hai</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Fully-Armed Motorbike</t>
+          <t>Xe Máy Vũ Trang Đầy Đủ</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>The Ending Cô ấy Saw</t>
+          <t>Kết Cục Nàng Chứng Kiến</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>This Path Cô ấy Missed</t>
+          <t>Con Đường Nàng Bỏ Lỡ</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Matrix Visitor: Safari Hunter</t>
+          <t>Du Khách Ma Trận: Thợ Săn Safari</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Matrix Visitor: Vigilante</t>
+          <t>Du Khách Ma Trận: Kẻ Phục Thù</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Matrix Visitor: Terminator</t>
+          <t>Du Khách Ma Trận: Sát Thủ</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Nhân Chứng Của Kết Thúc Vô Tận</t>
+          <t>Nhân Chứng Của Hư Vô Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Người Quan Sát Của Kết Thúc Vô Tận</t>
+          <t>Kẻ Canh Gác Của Hư Vô Vô Tận</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Kẻ Mưu Tính Của Kết Thúc Vô Tận</t>
+          <t>Kẻ Dệt Nên Vô Tận</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Negative Positive Retiral</t>
+          <t>Thoái lui Tích cực/Tiêu cực</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Ripper Demon</t>
+          <t>Ác Quỷ Xé Rách</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Miệng Ơi, Miệng Ở Đâu?</t>
+          <t>Miệng Ơi Miệng Đâu Rồi?</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>The Hatter</t>
+          <t>Thợ Làm Mũ</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Learn My True Name</t>
+          <t>Học Tên Thật Của Ta</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Who Am I</t>
+          <t>Ta Là Ai</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>My Way Home</t>
+          <t>Con Đường Về Nhà Ta</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Không Dreams, Không Illusions</t>
+          <t>Không mộng, không ảo</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Dreamless, Flawless</t>
+          <t>Dreamless, Hoàn Mỹ</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>In Rover We Trust</t>
+          <t>Tin vào Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>The Unquestioned Victory</t>
+          <t>Chiến Thắng Không Bàn Cãi</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Card Collector: Lahai-Roi</t>
+          <t>Nhà sưu tập Thẻ: Lahai-Roi</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Startorch Duelist</t>
+          <t>Duelist Sao Chổi</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tất cả-Terrain Void Storm Trooper</t>
+          <t>Lính Bão Hư Không Đa Địa Hình</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Iron-Blooded Husk</t>
+          <t>Xác Sống Máu Lạnh</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Lính Bão Hư Không Vùng Đất Băng Giá Loại I</t>
+          <t>Lính Tuần Bão Hư Không Vùng Đất Băng Loại I</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Lính Bão Hư Không Vùng Đất Băng Giá Loại II</t>
+          <t>Lính Tuần Bão Hư Không Vùng Đất Băng Loại II</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Frostlands Void Storm Trooper Type III</t>
+          <t>Lính Tuần Bão Hư Không Vùng Đất Băng Loại III</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Frostlands Void Storm Trooper Type IV</t>
+          <t>Lính Tuần Bão Hư Không Vùng Đất Băng Loại IV</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Frostlands Void Storm Trooper Type V</t>
+          <t>Lính Tuần Bão Hư Không Vùng Đất Băng Loại V</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Frostlands Tất cả-Terrain Void Storm Trooper</t>
+          <t>Lính Bão Hư Không Địa Hình Vùng Băng Giá</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Đánh bại Ashild trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Ashild trong "Đỉnh Danh Vọng: Cuộc Đọ Sức Nảy Lửa"</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Đánh bại Dennis trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Dennis trong "Đỉnh Danh Vọng: Trận Tái Đấu"</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Đánh bại Festa trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Festa trong "Đỉnh Danh Vọng: Cuộc Đọ Sức Tái Sinh"</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Đánh bại Chessa trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Chessa trong "Đỉnh Danh Vọng: Cuộc Đọ Sức Nảy Lửa"</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Đánh bại Calith trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Calith trong "Đỉnh Danh Vọng: Trận Tái Đấu".</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Đánh bại Anita trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đánh bại Anita trong "Đỉnh Danh Vọng: Cuộc Đọ Sức Tái Ngộ"</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Đạt Cấp Hạng 1 với danh hiệu "Qualified Duelist"</t>
+          <t>Đạt Cấp Bậc 1 với danh hiệu "Duelist Đủ Tiêu Chuẩn"</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Đạt Cấp Hạng 2 với danh hiệu "Certified Duelist"</t>
+          <t>Đạt Cấp Bậc 2 với danh hiệu "Duelist Chính Thức"</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Đạt Cấp Hạng 3 với danh hiệu "Certified Duelist"</t>
+          <t>Đạt Cấp Bậc 3 với danh hiệu "Duelist Đã Xác Nhận"</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Đạt Cấp Hạng 4 với danh hiệu "Promising Duelist"</t>
+          <t>Đạt Cấp Bậc 4 với danh hiệu "Duelist Đầy Triển Vọng"</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 5 với tư cách "Duelist Đầy Hứa Hẹn"</t>
+          <t>Đạt Cấp Bậc 5 với danh hiệu "Duelist Đầy Triển Vọng"</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 6 với tư cách "Duelist Kinh Nghiệm"</t>
+          <t>Đạt Cấp Bậc 6 với danh hiệu "Duelist Dày Dạn"</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 7 với tư cách "Duelist Kinh Nghiệm"</t>
+          <t>Đạt Cấp Bậc 7 với danh hiệu "Duelist Dày Dạn"</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 8 với tư cách "Duelist Nổi Tiếng"</t>
+          <t>Đạt Cấp Bậc 8 "Duelist Được Yêu Thích"</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 9 với tư cách "Popular Duelist"</t>
+          <t>Đạt Cấp Bậc 9 "Duelist Được Yêu Thích"</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Đạt Cấp Bậc 10 với tư cách "Duelist Lão Luyện"</t>
+          <t>Đạt Cấp Bậc 10 với danh hiệu "Duelist Kì Cựu"</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Hoàn thành Nhiệm Vụ Sự Kiện "Đỉnh Danh Vọng: Cuộc Đấu Tái Khởi".</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Thử Thách</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Vista View</t>
+          <t>Góc Nhìn Bao Quát</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ghi Chép</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Hyvatia's Eye</t>
+          <t>Con Mắt Hyvatia</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Sigil of the Nine Stars</t>
+          <t>Ấn Tín Cửu Tinh</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Non-Ideal Light Source</t>
+          <t>Nguồn Sáng Không Lý Tưởng</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>The Shape of Light</t>
+          <t>Hình Hài Ánh Sáng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Flight Over Sand</t>
+          <t>Bay Trên Sa Mạc</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Shadow of the Void</t>
+          <t>Bóng Tối Vô Tận</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Renewable Energy</t>
+          <t>Năng Lượng Tái Tạo</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>May's Frenzy</t>
+          <t>Cơn Cuồng Nộ Tháng Năm</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Until Không Stone Stands to Defy</t>
+          <t>Cho Đến Khi Không Còn Hòn Đá Nào Dám Chống Lại</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Blanket Search</t>
+          <t>Lùng Sục Toàn Bộ</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Bạn bè to Foes</t>
+          <t>Từ bạn thành thù</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Touch Training</t>
+          <t>Chạm vào Huấn Luyện</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Footnotes on Force</t>
+          <t>Chú giải về Lực</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Pointy Head</t>
+          <t>Đầu Nhọn</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Concord in Dance</t>
+          <t>Hòa Nhịp Khiêu Vũ</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Fluffguin Stone</t>
+          <t>Đá Chim cánh cụt bông</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Skelecanth and Mouse</t>
+          <t>Skelecanth và Chuột</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Children of the Snow</t>
+          <t>Những Đứa Con Tuyết</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Hoàn thành Giai Đoạn Platform của "Operation: Frontier Renewal"</t>
+          <t>Hoàn thành Giai Đoạn Nền Tảng của "Chiến Dịch: Tái Thiết Biên Cương"</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đạt 10,000 điểm trong Stability Accords ở "Doubled Pawns Matrix: Pilot"</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định ở "Ma Trận Tốt Đôi: Phi Công"</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá"</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Ode to the Second Sunrise"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Khúc Ca Bình Minh Thứ Hai"</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hoàn thành xây dựng lại Spacetrek Observatory trong "Operation: Frontier Renewal"</t>
+          <t>Xây dựng lại hoàn toàn Đài Thiên văn Spacetrek trong "Chiến dịch: Tái thiết Biên giới"</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đạt Cấp Rank 8 trong "Peaks of Prestige: Rekindled Duel"</t>
+          <t>Đạt Cấp Bậc 8 trong "Đỉnh Danh Vọng: Duel Tái Sinh"</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đạt 50% Tiến Độ Thám Hiểm ở bất kỳ 6 khu vực nào tại Lahai-Roi</t>
+          <t>Hoàn thành 50% Tiến Độ Thám Hiểm ở bất kỳ 6 khu vực nào thuộc Lahai-Roi</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đạt 50% Tiến Độ Thám Hiểm ở bất kỳ 9 khu vực nào tại Lahai-Roi</t>
+          <t>Hoàn thành 50% Tiến Độ Thám Hiểm tại 9 khu vực bất kỳ ở Lahai-Roi</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 1.000 Điểm Hoạt Động</t>
+          <t>Đạt tổng cộng 1.000 Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Fusion</t>
+          <t>Vực Sâu Chìm: Fusion</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Fusion</t>
+          <t>Tàn Dư Lửa Cháy: Fusion</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Fusion</t>
+          <t>Vùng Đất Chết: Fusion</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Spectro</t>
+          <t>Vực Sâu Chìm: Spectro</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Spectro</t>
+          <t>Tàn Dư Lửa Cháy: Spectro</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Spectro</t>
+          <t>Vùng Đất Chết: Spectro</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Electro</t>
+          <t>Vực Sâu Chìm: Electro</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Electro</t>
+          <t>Tàn Dư Lửa Cháy: Electro</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Electro</t>
+          <t>Vùng Đất Chết: Electro</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Aero</t>
+          <t>Vực Sâu Chìm: Aero</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Aero</t>
+          <t>Tàn Dư Lửa Cháy: Aero</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Aero</t>
+          <t>Vùng Đất Chết: Aero</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Sunken Abyss: Havoc</t>
+          <t>Vực Sâu Chìm: Havoc</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Flaming Remnants: Havoc</t>
+          <t>Tàn Dư Lửa Cháy: Havoc</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Doomed Wasteland: Havoc</t>
+          <t>Vùng Đất Chết: Havoc</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Hướng Dẫn Nhanh Tăng Cấp Modding</t>
+          <t>Hướng dẫn nhanh nâng cấp Modding</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bạn có thể tăng cấp Modding hiệu quả bằng các cách sau:</t>
+          <t>Bạn có thể tăng Cấp Độ Mod theo những cách sau:</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>"Rain Master"</t>
+          <t>"Bậc Thầy Mưa Gió"</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>"The Professor"</t>
+          <t>"Giáo Sư"</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>"Sun Chaser"</t>
+          <t>"Kẻ Đuổi Theo Ánh Mặt Trời"</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>"Leg Power Bike"</t>
+          <t>"Xe Đạp Sức Mạnh Chân"</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>"Quantic Leap"</t>
+          <t>"Bước Nhảy Lượng Tử"</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>"White Comet"</t>
+          <t>"Sao Chổi Trắng"</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>"Déjà vu"</t>
+          <t>"Ảo giác"</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>"Handbrake Turn"</t>
+          <t>"Quay xe gấp"</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Huafeng</t>
+          <t>Hoa Phong</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>"Rain Master"</t>
+          <t>"Bậc Thầy Mưa Gió"</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>"White Comet"</t>
+          <t>"Sao Chổi Trắng"</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Startorch Avenue</t>
+          <t>Đại lộ Startorch</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>River Nhảy</t>
+          <t>Nhảy Qua Sông</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Valley Dash</t>
+          <t>Đường Đua Vực Sâu</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>"Sunglasses"</t>
+          <t>"Kính Râm"</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Bên Vực Sâu</t>
+          <t>Nhân danh Hư Vực...</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Slalom Drive</t>
+          <t>Đường Đua Zíc-zắc</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Classic Circuit</t>
+          <t>Mạch Cổ Điển</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Hoàn Thành Chương III Nhiệm Vụ Chính</t>
+          <t>Tiến triển Nhiệm vụ Chính Chương III</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Mở Rương Cung Cấp tại Lahai-Roi</t>
+          <t>Mở Rương Vật Tư tại Lahai-Roi</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Boss tại Lahai-Roi</t>
+          <t>Hoàn thành Thử Thách Trùm tại Lahai-Roi</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Clear Void Storm Zones</t>
+          <t>Dọn sạch Khu Bão Hư Không</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Thách Thức Tổ Tacet Discord</t>
+          <t>Thử Thách Tổ Tacet Discord</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Novelty Rush I</t>
+          <t>Cơn Sốt Mới Lạ I</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Trickshot I</t>
+          <t>Bắn tỉa I</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Full Attunement I</t>
+          <t>Điều Tiết Hoàn Toàn I</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Reconstructor I</t>
+          <t>Kỹ Sư Tái Cấu Trúc Cấp I</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Primal Instinct I</t>
+          <t>Bản Năng Nguyên Thủy I</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Overcharge I</t>
+          <t>Quá Tải I</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Novelty Rush II</t>
+          <t>Cơn Sốt Mới Lạ II</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Trickshot II</t>
+          <t>Bắn tỉa II</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Full Attunement II</t>
+          <t>Điều Tiết Hoàn Toàn II</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Reconstructor II</t>
+          <t>Kỹ Sư Tái Cấu Trúc Cấp II</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Primal Instinct II</t>
+          <t>Bản Năng Nguyên Thủy II</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Overcharge II</t>
+          <t>Quá Tải II</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Novelty Rush III</t>
+          <t>Cơn Sốt Mới Lạ III</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Trickshot III</t>
+          <t>Bắn tỉa III</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Full Attunement III</t>
+          <t>Điều Tiết Hoàn Toàn III</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Reconstructor III</t>
+          <t>Kỹ Sư Tái Cấu Trúc Cấp III</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Primal Instinct III</t>
+          <t>Bản Năng Nguyên Thủy III</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Overcharge III</t>
+          <t>Quá Tải III</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Novelty Rush</t>
+          <t>Cơn Sốt Mới Lạ</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Trickshot</t>
+          <t>Bắn tỉa</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Full Attunement</t>
+          <t>Điều Tiết Hoàn Toàn</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Reconstructor</t>
+          <t>Kỹ Sư Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Primal Instinct</t>
+          <t>Bản Năng Nguyên Thủy</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Overcharge</t>
+          <t>Quá Tải</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Blade Reforged I</t>
+          <t>Kiếm Tái Luyện I</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Glorybound I</t>
+          <t>Vinh Quang I</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Tấn Công</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Energy Consumption Rate</t>
+          <t>Tốc Độ Tiêu Hao Năng Lượng</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Initial Force Field Strength</t>
+          <t>Cường Độ Trường Lực Ban Đầu</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Force Field Regen Rate</t>
+          <t>Tốc Độ Hồi Phục Khiên Lực</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Thẻ Học Sinh</t>
+          <t>Thẻ học sinh</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Cục</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Rabelle College</t>
+          <t>Học Viện Rabelle</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Diễn văn</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Leonidas Hotel</t>
+          <t>Khách sạn Leonidas</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Enable Navigation</t>
+          <t>Bật Chỉ Đường</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Disable Navigation</t>
+          <t>Vô Hiệu Hóa Hệ Thống Dẫn Đường</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Không thể điều hướng ở khu vực này</t>
+          <t>Khu vực này không hỗ trợ định vị</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Không thể sử dụng Chế Độ Tự Lái ở trạng thái hiện tại</t>
+          <t>Không thể sử dụng Chế độ Tự lái ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Con đường này không hỗ trợ Chế Độ Tự Lái Lặp Lại</t>
+          <t>Đường này không hỗ trợ Chế Độ Tự Lái Vòng Lặp</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Autopilot Mode Off</t>
+          <t>Chế Độ Lái Tự Động Đã Tắt</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Autopilot Mode</t>
+          <t>Chế Độ Tự Lái</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Looped Autopilot Mode</t>
+          <t>Chế Độ Tự Lái Lặp Lại</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Hiện không thể điều hướng</t>
+          <t>Hệ thống định vị hiện không khả dụng</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Time Draws Near</t>
+          <t>Thời Gian Sắp Đến</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Infinite Visability</t>
+          <t>Tầm Nhìn Vô Biên</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Weapons Free</t>
+          <t>Vũ khí miễn phí</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Lunar Sequence</t>
+          <t>Trình Tự Mặt Trăng</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Tầm Nhìn Của Sợi Chỉ</t>
+          <t>Tầm Nhìn Sợi Chỉ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Săn Lùng Không Ngừng Nghỉ</t>
+          <t>Săn không hồi kết</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Bậc 2 với danh hiệu "Duelist Đã Xác Minh"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 2 "Duelist Đã Xác Nhận."</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Bậc 5 với danh hiệu "Duelist Nổi Tiếng"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 5 "Duelist Nổi Tiếng."</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Bậc 6 với danh hiệu "Duelist Kì Cựu"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 6 "Duelist Kì Cựu"</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 7 với danh hiệu "Tất cả-Star Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 7 "Duelist Toàn Sao"</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 8 với danh hiệu "Legendary Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 8 "Duelist Huyền Thoại"</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 9 với danh hiệu "Legendary Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 9 "Duelist Huyền Thoại"</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 3 với danh hiệu "Promising Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 3 "Duelist Đầy Triển Vọng."</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 4 với danh hiệu "Experienced Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 4 "Duelist Kinh Nghiệm."</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đạt Cấp Rank 4 với danh hiệu "Experienced Duelist"</t>
+          <t>Mở khóa sau khi đạt Cấp Bậc 4 "Duelist Kinh Nghiệm."</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Iuno's Tactics Unlocked</t>
+          <t>Chiến Thuật Của Iuno Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Chisa's Tactics Unlocked</t>
+          <t>Chiến thuật của Chisa đã mở khóa</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Galbrena's Tactics Unlocked</t>
+          <t>Đã Mở Khóa Chiến Thuật Của Galbrena</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Chọn Thẻ để Triển khai</t>
+          <t>Chọn Thẻ để Triển Khai</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chọn Thẻ để Trộn lại</t>
+          <t>Chọn Thẻ để Xáo Trộn Lại</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Basic Livery</t>
+          <t>Mẫu Sơn Cơ Bản</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Preset: Shine Brighter</t>
+          <t>Bản dựng sẵn: Tỏa sáng rực rỡ</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Chọn Thẻ để Tái cấu trúc</t>
+          <t>Chọn Thẻ để Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Blade Reforged II</t>
+          <t>Kiếm Tái Luyện II</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Glorybound II</t>
+          <t>Vinh Quang II</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Blade Reforged III</t>
+          <t>Kiếm Tái Luyện III</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Glorybound III</t>
+          <t>Vinh Quang III</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Blade Reforged</t>
+          <t>Kiếm Tái Luyện</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14</t>
+          <t>Đạt Cấp Độ Liên Minh 14</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Qualified Duelist</t>
+          <t>Duelist Đủ Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Certified Duelist</t>
+          <t>Duelist Chính Hiệu</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Promising Duelist</t>
+          <t>Duelist Giữ Lời</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Experienced Duelist</t>
+          <t>Duelist Lão Luyện</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Popular Duelist</t>
+          <t>Đấu sĩ Nổi tiếng</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Veteran Duelist</t>
+          <t>Duelist Lão Thành</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tất cả-Star Duelist</t>
+          <t>Duelist Toàn Sao</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Legendary Duelist</t>
+          <t>Đấu Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Attunement</t>
+          <t>Hòa điệu</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Rally</t>
+          <t>Tập Hợp</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Enhanced Rally</t>
+          <t>Hồi Sinh Cường Hóa</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Dùng Lynae để vượt Tháp Nguy Hiểm từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
+          <t>Dùng Lynae để vượt qua Tháp Hazard Tầng 1 đến Tầng 4 trong Khu Vực Thử Thách: Vùng Nguy Hiểm.</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dùng Mornye để vượt Tháp Nguy Hiểm từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
+          <t>Dùng Mornye để vượt qua Tháp Hazard Tầng 1 đến Tầng 4 trong Khu Vực Thử Thách: Vùng Nguy Hiểm.</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Dùng Augusta để vượt Tháp Nguy Hiểm từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
+          <t>Dùng Augusta để vượt từ tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Dùng Lynae để vượt Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Lynae để vượt qua Vùng Nước Tái Sinh: Dòng Chảy Cuồng Nộ tại Whimpering Wastes.</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Dùng Mornye để vượt Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Mornye để dọn sạch Vùng Nước Tái Sinh: Dòng Chảy ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Dùng Augusta hoặc Carlotta để vượt Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Augusta hoặc Carlotta để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia hoặc Zani để vượt Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Cartethyia hoặc Zani để vượt ải "Nước Tái Sinh: Dòng Chảy" tại Whimpering Wastes</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Dùng Galbrena hoặc Phrolova để vượt Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Galbrena hoặc Phrolova để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Dùng bất kỳ đội nào để hoàn thành Stability Accords trong "Doubled Pawns Matrix: Pilot"</t>
+          <t>Dùng bất kỳ đội hình nào hoàn thành Hiệp Ước Ổn Định trong "Ma Trận Tốt Đôi: Thí Điểm"</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Dùng Lynae hoàn thành mỗi khu huấn luyện một lần</t>
+          <t>Dùng Lynae để hoàn thành từng khu huấn luyện một lần.</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Dùng Mornye hoàn thành mỗi khu huấn luyện một lần</t>
+          <t>Dùng Mornye hoàn thành từng khu huấn luyện ba lần</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Hoàn thành "Đỉnh Danh Vọng: Trận Tái Đấu" Giai Đoạn 18</t>
+          <t>Hoàn thành Giai Đoạn 18 "Đỉnh Danh Vọng: Cuộc Đọ Sức Trở Lại"</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đạt Cấp Hội 8</t>
+          <t>Đạt Cấp Độ Liên Minh 8</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nhận 1 Điểm Mod</t>
+          <t>Nhận được 1 Điểm Nâng Cấp</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Nhận 4 Điểm Mod</t>
+          <t>Thu thập 4 Điểm Cải Tiến</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Nhận 8 Điểm Mod</t>
+          <t>Thu thập 8 Điểm Nâng Cấp</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Nhận 12 Điểm Mod</t>
+          <t>Nhận được 12 Điểm Cải Tạo</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Nhận giấy phép phương tiện</t>
+          <t>Nhận giấy phép sử dụng phương tiện</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đạt Cấp Modding 5</t>
+          <t>Đạt Cấp Độ Modding 5</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đạt Cấp Modding 10</t>
+          <t>Đạt Cấp Độ Modding 10</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Đạt Cấp Modding 15</t>
+          <t>Đạt Cấp Độ Modding 15</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Nhận 5.000 Điểm Kinh Nghiệm Modding từ Rương Cung Ứng</t>
+          <t>Nhận 5.000 Điểm Kinh Nghiệm Nâng Cấp từ Rương Cung Ứng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Singularity Expansion đã mở khóa</t>
+          <t>Đã Mở Khóa Mở Rộng Kỳ Dị</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Doubled Pawns Matrix: Pilot bị khóa</t>
+          <t>Ma trận Tốt Đôi: Phi Công Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Phần thưởng khả thi</t>
+          <t>Những Phần Thưởng Khả Thi</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đánh bại Ashild trong trận đấu để nhận</t>
+          <t>Đánh bại Ashild trong trận đấu để nhận được</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Đánh bại Dennis trong trận đấu để nhận</t>
+          <t>Đánh bại Dennis trong một trận đấu để nhận</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Đánh bại Festa trong trận đấu để nhận</t>
+          <t>Đánh bại Festa trong một trận đấu tay đôi để nhận được</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Đánh bại Chessa trong trận đấu để nhận</t>
+          <t>Đánh bại Chessa trong cuộc đấu để nhận được</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Đánh bại Calith trong trận đấu để nhận</t>
+          <t>Đánh bại Calith trong một trận đấu để nhận được.</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Đánh bại Anita trong trận đấu để nhận</t>
+          <t>Đánh bại Anita trong một trận đấu để nhận được</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đánh bại Aya trong trận đấu để nhận</t>
+          <t>Đánh bại Aya trong trận đấu để nhận được</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Đánh bại Zahira trong trận đấu để nhận</t>
+          <t>Đánh bại Zahira trong trận đấu tay đôi để giành chiến thắng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Đánh bại Lagerith trong trận đấu để nhận</t>
+          <t>Đánh bại Lagerith trong một trận đấu tay đôi để nhận được</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Đánh bại Katrina trong trận đấu để nhận</t>
+          <t>Đánh bại Katrina trong một trận đấu tay đôi để nhận được</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đặc Tính Đấu Thủ</t>
+          <t>Duelist Traits</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
